--- a/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
+++ b/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mengpin.ge\World Resources Institute\TRAC City - HK 2050 is now\EPS HK 2.0\eps-hongkong-develop\InputData\elec\DPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daiyang.zhang\Desktop\eps-us-3.4.7 working_D1904_T0858_woking\eps-us-3.4.7 HK working\InputData\elec\DPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="11_D266362D8FF193AA0856DF8B26466D6157EF2312" xr6:coauthVersionLast="41" xr6:coauthVersionMax="45" xr10:uidLastSave="{BA5A0638-4367-4F8A-BFFE-4509B8BEAE35}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98D2C4F2-6AD9-4846-914C-9EC446235243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="1095" windowWidth="19230" windowHeight="13050" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="DPbES" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -134,7 +139,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,13 +151,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="6"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -178,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -187,7 +185,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -206,9 +203,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -246,9 +243,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -281,26 +278,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -333,26 +313,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -527,84 +490,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -621,13 +584,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AK17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>32</v>
       </c>
@@ -740,7 +703,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -755,581 +718,584 @@
         <f t="shared" ref="D2:AK9" si="0">$B2</f>
         <v>2</v>
       </c>
-      <c r="E2" s="4">
-        <v>3</v>
-      </c>
-      <c r="F2" s="4">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4">
-        <v>4</v>
-      </c>
-      <c r="H2" s="4">
-        <f>G2</f>
-        <v>4</v>
-      </c>
-      <c r="I2" s="4">
-        <f t="shared" ref="I2:AK2" si="1">H2</f>
-        <v>4</v>
-      </c>
-      <c r="J2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="M2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="N2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="O2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="P2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="Q2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="R2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="S2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="U2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="V2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="W2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="X2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="Y2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="Z2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AA2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AB2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AC2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AD2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AE2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AF2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AG2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AH2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AI2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AJ2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="AK2" s="4">
-        <f t="shared" si="1"/>
-        <v>4</v>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Q2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="R2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="V2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AB2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AC2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AE2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AF2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AG2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AI2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AJ2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AK2">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:R12" si="2">$B3</f>
-        <v>1</v>
+        <f t="shared" ref="C3:R17" si="1">$B3</f>
+        <v>2</v>
       </c>
       <c r="D3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="E3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="F3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="G3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="I3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="K3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="L3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="M3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="N3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="O3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="P3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="R3">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="S3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <f t="shared" si="2"/>
-        <v>5</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="X5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AA5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AD5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AF5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AG5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AI5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AJ5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AK5">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1337,7 +1303,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D6">
@@ -1477,7 +1443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1485,7 +1451,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D7">
@@ -1625,7 +1591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1633,7 +1599,7 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D8">
@@ -1773,155 +1739,155 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C9">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="X9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Y9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AA9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AB9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="AJ9">
+        <f t="shared" ref="AJ9:AK17" si="2">$B9</f>
+        <v>2</v>
+      </c>
+      <c r="AK9">
         <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="F9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="L9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="M9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="N9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="O9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="P9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="W9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="X9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Y9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="Z9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AA9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AB9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AC9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AD9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AE9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AF9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AG9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AH9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AI9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="AJ9">
-        <f t="shared" ref="D9:AK12" si="3">$B9</f>
-        <v>5</v>
-      </c>
-      <c r="AK9">
-        <f t="shared" si="3"/>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1929,71 +1895,71 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="D10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="I10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="K10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="M10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="N10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="O10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="P10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="R10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="S10">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="S10:AK17" si="3">$B10</f>
         <v>2</v>
       </c>
       <c r="T10">
@@ -2069,155 +2035,155 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>17</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="D11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="E11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="F11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="G11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="I11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="J11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="K11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="L11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="M11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="N11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="O11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="P11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="R11">
-        <f t="shared" si="3"/>
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="S11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK11">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -2225,67 +2191,67 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="D12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="F12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="G12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="I12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="L12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="M12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="N12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="P12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="S12">
@@ -2365,746 +2331,744 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13">
-        <f>B2</f>
         <v>2</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:AK13" si="4">C2</f>
+        <f>$B13</f>
         <v>2</v>
       </c>
       <c r="D13">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E13">
-        <f t="shared" si="4"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="F13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="G13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="I13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="K13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="L13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="M13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="N13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="O13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="P13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="R13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="S13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="T13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="U13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="V13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="W13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="X13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="4"/>
-        <v>4</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
       <c r="B14">
-        <f>B6</f>
         <v>2</v>
       </c>
       <c r="C14">
-        <f t="shared" ref="C14:AK14" si="5">C6</f>
+        <f>$B14</f>
         <v>2</v>
       </c>
       <c r="D14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="I14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="K14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="M14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="N14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="O14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="P14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="R14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="S14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="T14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="V14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="W14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="X14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="Z14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AA14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AB14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AC14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AD14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AE14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AG14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AH14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AI14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AJ14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AK14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>29</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C15">
-        <f t="shared" ref="C15:AK15" si="6">C11</f>
+        <f t="shared" ref="C15:C17" si="4">$B15</f>
         <v>2</v>
       </c>
       <c r="D15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="I15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="K15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="M15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="N15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="O15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="P15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="R15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="S15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="T15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="V15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="W15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="X15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="Z15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AA15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AB15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AC15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AD15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AE15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AF15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AG15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AH15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AI15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AJ15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AK15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C16">
-        <f t="shared" ref="C16:AK16" si="7">C11</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="D16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="F16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="G16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="H16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="I16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="J16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="K16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="L16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="M16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="N16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="O16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="P16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="R16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="S16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="T16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="U16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="V16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="W16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="X16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="Z16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AA16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AB16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AC16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AD16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AE16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AF16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AG16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AH16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AI16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AJ16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="AK16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>31</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
-        <f>$B$17</f>
-        <v>3</v>
+        <f t="shared" si="4"/>
+        <v>2</v>
       </c>
       <c r="D17">
-        <f t="shared" ref="D17:AK17" si="8">$B$17</f>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="E17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="F17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="G17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="H17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="I17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="J17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="K17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="L17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="M17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="N17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="O17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="P17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="R17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
       <c r="S17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="T17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="U17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="V17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="W17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="X17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="Z17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AA17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AB17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AC17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AD17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AE17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AF17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AI17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AJ17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
       <c r="AK17">
-        <f t="shared" si="8"/>
-        <v>3</v>
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3113,40 +3077,41 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3154,24 +3119,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -3190,70 +3216,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -3355,35 +3334,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E221A8A-B9D9-4D58-9CC4-C52681123A8E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B94B21AE-F067-4785-B6E0-D7C9F0BE3C99}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{358C1F4D-4B63-4704-9A42-2490BF3F25B3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCD4E2AF-EAF2-4EB0-AFA7-61018B566002}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -3392,12 +3359,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDA91C13-4E66-4724-9EB9-720D0A047543}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>